--- a/신고신저가_20260727.xlsx
+++ b/신고신저가_20260727.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="00C00000"/>
     </font>
@@ -76,16 +77,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -454,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -612,7 +617,42 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 글로벌 반도체·AI하드웨어 동반 조정, 금융·리츠·방어주로 순환매 국면 (테크 차익실현 성격 추정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>■ 美: S&amp;P +0.05%·나스닥 -0.64% 혼조 — 금융(순강도 +18)·리츠(XLRE +2.2%)·소재(XLB +1.9%) 강세 vs 테크(XLK -1.4%) 유일 약세. 테넷헬스케어(+17%)·디지털리얼티 실적서프라이즈로 신고가, 글로벌파운드리스·코닝·블룸에너지 신저가</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 日: 닛케이 -2.73% 급락 — 은행 등 금융 신고가 9개에도 디스코 -12%(반도체장비 가이던스 실망) 등 전기·정밀 약세가 지수 주도</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>■ 中·홍콩: 상해 -1.61%·CSI300 -1.67%·항셍 -0.98%·항셍테크 -1.47% 동반 하락, 반도체·테크 약세. 더밍리(스토리지모듈) 8거래일 6하한가 지속</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ①7/28 코닝 실적·美 빅테크 어닝 시즌 ②반도체 조정 지속 여부 ③글로벌 금융·방어주 순환매 연속성</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -710,19 +750,19 @@
       <c r="C2" t="n">
         <v>7411.98</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="5" t="n">
         <v>-0.61</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="4" t="n">
         <v>0.73</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="4" t="n">
         <v>4.27</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="4" t="n">
         <v>8.279999999999999</v>
       </c>
       <c r="I2" t="n">
@@ -748,19 +788,19 @@
       <c r="C3" t="n">
         <v>24975.82</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="5" t="n">
         <v>-0.64</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="5" t="n">
         <v>-2.13</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="5" t="n">
         <v>-1.97</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>2.2</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="4" t="n">
         <v>7.46</v>
       </c>
       <c r="I3" t="n">
@@ -786,19 +826,19 @@
       <c r="C4" t="n">
         <v>6690.62</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="5" t="n">
         <v>-5.72</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>-1.91</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="5" t="n">
         <v>-21.02</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="4" t="n">
         <v>4.73</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="4" t="n">
         <v>58.76</v>
       </c>
       <c r="I4" t="n">
@@ -824,19 +864,19 @@
       <c r="C5" t="n">
         <v>64611.15</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="5" t="n">
         <v>-2.73</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="5" t="n">
         <v>-3.33</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="5" t="n">
         <v>-6.6</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="4" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="4" t="n">
         <v>28.35</v>
       </c>
       <c r="I5" t="n">
@@ -860,11 +900,11 @@
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
     </row>
@@ -880,11 +920,11 @@
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
     </row>
@@ -900,11 +940,11 @@
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
     </row>
@@ -920,11 +960,11 @@
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
     </row>
@@ -1023,7 +1063,7 @@
       <c r="F2" t="n">
         <v>18</v>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1058,7 +1098,7 @@
       <c r="F3" t="n">
         <v>7</v>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1093,7 +1133,7 @@
       <c r="F4" t="n">
         <v>7</v>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1128,7 +1168,7 @@
       <c r="F5" t="n">
         <v>6</v>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1163,7 +1203,7 @@
       <c r="F6" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1198,7 +1238,7 @@
       <c r="F7" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1233,7 +1273,7 @@
       <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1268,7 +1308,7 @@
       <c r="F9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1303,7 +1343,7 @@
       <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1338,7 +1378,7 @@
       <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1373,7 +1413,7 @@
       <c r="F12" t="n">
         <v>-1</v>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1408,7 +1448,7 @@
       <c r="F13" t="n">
         <v>-1</v>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1443,7 +1483,7 @@
       <c r="F14" t="n">
         <v>-2</v>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1478,7 +1518,7 @@
       <c r="F15" t="n">
         <v>-2</v>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1513,7 +1553,7 @@
       <c r="F16" t="n">
         <v>-2</v>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1548,7 +1588,7 @@
       <c r="F17" t="n">
         <v>-2</v>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1723,7 +1763,7 @@
       <c r="F22" t="n">
         <v>9</v>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1758,7 +1798,7 @@
       <c r="F23" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1793,7 +1833,7 @@
       <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1828,7 +1868,7 @@
       <c r="F25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1863,7 +1903,7 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1898,7 +1938,7 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1933,7 +1973,7 @@
       <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1968,7 +2008,7 @@
       <c r="F29" t="n">
         <v>-1</v>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2353,7 +2393,7 @@
       <c r="F40" t="n">
         <v>3</v>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2388,7 +2428,7 @@
       <c r="F41" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2423,7 +2463,7 @@
       <c r="F42" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G42" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2458,7 +2498,7 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2493,7 +2533,7 @@
       <c r="F44" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2528,7 +2568,7 @@
       <c r="F45" t="n">
         <v>-1</v>
       </c>
-      <c r="G45" s="6" t="inlineStr">
+      <c r="G45" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2563,7 +2603,7 @@
       <c r="F46" t="n">
         <v>-1</v>
       </c>
-      <c r="G46" s="6" t="inlineStr">
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2983,7 +3023,7 @@
       <c r="F58" t="n">
         <v>2</v>
       </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="G58" s="7" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3018,7 +3058,7 @@
       <c r="F59" t="n">
         <v>-1</v>
       </c>
-      <c r="G59" s="6" t="inlineStr">
+      <c r="G59" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3053,7 +3093,7 @@
       <c r="F60" t="n">
         <v>-1</v>
       </c>
-      <c r="G60" s="6" t="inlineStr">
+      <c r="G60" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3088,7 +3128,7 @@
       <c r="F61" t="n">
         <v>-1</v>
       </c>
-      <c r="G61" s="6" t="inlineStr">
+      <c r="G61" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3123,7 +3163,7 @@
       <c r="F62" t="n">
         <v>-2</v>
       </c>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3605,30 +3645,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3649,90 +3690,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -3754,58 +3800,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="7" t="n">
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>테크 -1.4%, 당일 유일 하락 섹터 — AI·반도체 차익실현(GFS·GLW 신저가)</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="n">
         <v>-1.4</v>
       </c>
-      <c r="E2" s="7" t="n">
+      <c r="F2" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="F2" s="7" t="n">
+      <c r="G2" s="10" t="n">
         <v>-3.9</v>
       </c>
-      <c r="G2" s="7" t="n">
+      <c r="H2" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="H2" s="7" t="n">
+      <c r="I2" s="10" t="n">
         <v>22.5</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="7" t="n">
+      <c r="K2" s="10" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="7" t="n">
+      <c r="M2" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="7" t="n">
+      <c r="O2" s="10" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="7" t="n">
+      <c r="Q2" s="10" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="7" t="n">
+      <c r="S2" s="10" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="7" t="n">
+      <c r="U2" s="10" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3825,58 +3876,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>헬스케어 +0.7%, 테넷헬스케어 실적 서프라이즈 등 방어주 순환매</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="F3" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="G3" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="H3" s="10" t="n">
         <v>11.7</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="I3" s="10" t="n">
         <v>5.9</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>8</v>
       </c>
-      <c r="J3" s="7" t="n">
+      <c r="K3" s="10" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="7" t="n">
+      <c r="M3" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="7" t="n">
+      <c r="O3" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="7" t="n">
+      <c r="Q3" s="10" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="7" t="n">
+      <c r="S3" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="7" t="n">
+      <c r="U3" s="10" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3896,58 +3952,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>금융 +0.9%, 신고-신저 순강도 +18로 시장 최강 섹터, 은행 실적 호조</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="F4" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="G4" s="10" t="n">
         <v>4.8</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="H4" s="10" t="n">
         <v>9.1</v>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="I4" s="10" t="n">
         <v>3.7</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>9</v>
       </c>
-      <c r="J4" s="7" t="n">
+      <c r="K4" s="10" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="7" t="n">
+      <c r="M4" s="10" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="7" t="n">
+      <c r="O4" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="7" t="n">
+      <c r="Q4" s="10" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="7" t="n">
+      <c r="S4" s="10" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="7" t="n">
+      <c r="U4" s="10" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -3967,58 +4028,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>경기소비재 +0.6%, 주간 -5.2% 부진 딛고 당일 반등</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="F5" s="10" t="n">
         <v>-5.2</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="G5" s="10" t="n">
         <v>-4.9</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="H5" s="10" t="n">
         <v>-6.9</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="I5" s="10" t="n">
         <v>-8</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="7" t="n">
+      <c r="K5" s="10" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="7" t="n">
+      <c r="M5" s="10" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="7" t="n">
+      <c r="O5" s="10" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="7" t="n">
+      <c r="Q5" s="10" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="7" t="n">
+      <c r="S5" s="10" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="7" t="n">
+      <c r="U5" s="10" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4038,58 +4104,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>커뮤니케이션 +0.9%, 대형 인터넷주 조정 속 통신주 반등</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="F6" s="10" t="n">
         <v>-3.9</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="G6" s="10" t="n">
         <v>-0.2</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="H6" s="10" t="n">
         <v>-9.199999999999999</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="I6" s="10" t="n">
         <v>-9.199999999999999</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="K6" s="10" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="7" t="n">
+      <c r="M6" s="10" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="7" t="n">
+      <c r="O6" s="10" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="7" t="n">
+      <c r="Q6" s="10" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="7" t="n">
+      <c r="S6" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="7" t="n">
+      <c r="U6" s="10" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4109,58 +4180,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>산업재 +0.4%, RTX 방산·산업서비스 신고가로 견조</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="F7" s="10" t="n">
         <v>1.8</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="G7" s="10" t="n">
         <v>1.4</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="H7" s="10" t="n">
         <v>5.2</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="I7" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="7" t="n">
+      <c r="K7" s="10" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="7" t="n">
+      <c r="M7" s="10" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="7" t="n">
+      <c r="O7" s="10" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="7" t="n">
+      <c r="Q7" s="10" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="7" t="n">
+      <c r="S7" s="10" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="7" t="n">
+      <c r="U7" s="10" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4180,58 +4256,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>필수소비재 +1.1%, 테크 회피 자금 방어주 유입</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="n">
         <v>1.1</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="F8" s="10" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="10" t="n">
         <v>-0.4</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="H8" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="I8" s="10" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="7" t="n">
+      <c r="K8" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="7" t="n">
+      <c r="M8" s="10" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="7" t="n">
+      <c r="O8" s="10" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="7" t="n">
+      <c r="Q8" s="10" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="7" t="n">
+      <c r="S8" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="7" t="n">
+      <c r="U8" s="10" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4251,58 +4332,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>에너지 +0.4%, YTD +35% 연간 1위 유지·유가 강세</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="F9" s="10" t="n">
         <v>3.4</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="G9" s="10" t="n">
         <v>11.3</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="H9" s="10" t="n">
         <v>5.4</v>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="I9" s="10" t="n">
         <v>35.2</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="7" t="n">
+      <c r="K9" s="10" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="7" t="n">
+      <c r="M9" s="10" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="7" t="n">
+      <c r="O9" s="10" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="7" t="n">
+      <c r="Q9" s="10" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="7" t="n">
+      <c r="S9" s="10" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="7" t="n">
+      <c r="U9" s="10" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4322,58 +4408,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>유틸리티 +0.2%, 데이터센터 전력수요·방어 매력</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="F10" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="G10" s="10" t="n">
         <v>1.6</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="H10" s="10" t="n">
         <v>1.1</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="I10" s="10" t="n">
         <v>9.9</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>6</v>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="K10" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="M10" s="10" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="7" t="n">
+      <c r="O10" s="10" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="7" t="n">
+      <c r="Q10" s="10" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="7" t="n">
+      <c r="S10" s="10" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="7" t="n">
+      <c r="U10" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4393,58 +4484,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>소재 +1.9%, 당일 최강 상승 — 포장·화학주 반등</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="n">
         <v>1.9</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="F11" s="10" t="n">
         <v>1.4</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="G11" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="H11" s="10" t="n">
         <v>-0.7</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="I11" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>5</v>
       </c>
-      <c r="J11" s="7" t="n">
+      <c r="K11" s="10" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="7" t="n">
+      <c r="M11" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="7" t="n">
+      <c r="O11" s="10" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="7" t="n">
+      <c r="Q11" s="10" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="7" t="n">
+      <c r="S11" s="10" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="7" t="n">
+      <c r="U11" s="10" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4464,58 +4560,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>리츠 +2.2%, DLR 데이터센터 REIT 급등 주도로 섹터 최강</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="n">
         <v>2.2</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="F12" s="10" t="n">
         <v>1.2</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="G12" s="10" t="n">
         <v>3.2</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="H12" s="10" t="n">
         <v>5.4</v>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="I12" s="10" t="n">
         <v>15.6</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>4</v>
       </c>
-      <c r="J12" s="7" t="n">
+      <c r="K12" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="7" t="n">
+      <c r="M12" s="10" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="7" t="n">
+      <c r="O12" s="10" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="7" t="n">
+      <c r="Q12" s="10" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="7" t="n">
+      <c r="S12" s="10" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="7" t="n">
+      <c r="U12" s="10" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4535,58 +4636,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="9" t="inlineStr"/>
+      <c r="E13" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="F13" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="G13" s="10" t="n">
         <v>4.3</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="H13" s="10" t="n">
         <v>6.8</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="I13" s="10" t="n">
         <v>16.2</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>8</v>
       </c>
-      <c r="J13" s="7" t="n">
+      <c r="K13" s="10" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="7" t="n">
+      <c r="M13" s="10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="7" t="n">
+      <c r="O13" s="10" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="7" t="n">
+      <c r="Q13" s="10" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="7" t="n">
+      <c r="S13" s="10" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="7" t="n">
+      <c r="U13" s="10" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4606,58 +4708,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="9" t="inlineStr"/>
+      <c r="E14" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="F14" s="10" t="n">
         <v>6.4</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="G14" s="10" t="n">
         <v>10.2</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="H14" s="10" t="n">
         <v>-1.9</v>
       </c>
-      <c r="H14" s="7" t="n">
+      <c r="I14" s="10" t="n">
         <v>18.1</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>7</v>
       </c>
-      <c r="J14" s="7" t="n">
+      <c r="K14" s="10" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="M14" s="10" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="7" t="n">
+      <c r="O14" s="10" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="7" t="n">
+      <c r="Q14" s="10" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="7" t="n">
+      <c r="S14" s="10" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="7" t="n">
+      <c r="U14" s="10" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -4677,58 +4780,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="10" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="F15" s="10" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="G15" s="10" t="n">
         <v>-4.1</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="H15" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="H15" s="7" t="n">
+      <c r="I15" s="10" t="n">
         <v>10.2</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>10</v>
       </c>
-      <c r="J15" s="7" t="n">
+      <c r="K15" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="7" t="n">
+      <c r="M15" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="7" t="n">
+      <c r="O15" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="7" t="n">
+      <c r="Q15" s="10" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="7" t="n">
+      <c r="S15" s="10" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="7" t="n">
+      <c r="U15" s="10" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4748,58 +4852,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="9" t="inlineStr"/>
+      <c r="E16" s="10" t="n">
         <v>-2.3</v>
       </c>
-      <c r="E16" s="7" t="n">
+      <c r="F16" s="10" t="n">
         <v>-2.4</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="G16" s="10" t="n">
         <v>-0.7</v>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="H16" s="10" t="n">
         <v>6.1</v>
       </c>
-      <c r="H16" s="7" t="n">
+      <c r="I16" s="10" t="n">
         <v>21.8</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="7" t="n">
+      <c r="K16" s="10" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="7" t="n">
+      <c r="M16" s="10" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="7" t="n">
+      <c r="O16" s="10" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="7" t="n">
+      <c r="Q16" s="10" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="7" t="n">
+      <c r="S16" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="7" t="n">
+      <c r="U16" s="10" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4819,58 +4924,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="9" t="inlineStr"/>
+      <c r="E17" s="10" t="n">
         <v>2.4</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="F17" s="10" t="n">
         <v>2.8</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="G17" s="10" t="n">
         <v>5.7</v>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="H17" s="10" t="n">
         <v>-3.7</v>
       </c>
-      <c r="H17" s="7" t="n">
+      <c r="I17" s="10" t="n">
         <v>3.9</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>12</v>
       </c>
-      <c r="J17" s="7" t="n">
+      <c r="K17" s="10" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="7" t="n">
+      <c r="M17" s="10" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="7" t="n">
+      <c r="O17" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="7" t="n">
+      <c r="Q17" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="7" t="n">
+      <c r="S17" s="10" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="7" t="n">
+      <c r="U17" s="10" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4890,58 +4996,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="9" t="inlineStr"/>
+      <c r="E18" s="10" t="n">
         <v>-2.1</v>
       </c>
-      <c r="E18" s="7" t="n">
+      <c r="F18" s="10" t="n">
         <v>-1.3</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="G18" s="10" t="n">
         <v>6.8</v>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="H18" s="10" t="n">
         <v>-4.7</v>
       </c>
-      <c r="H18" s="7" t="n">
+      <c r="I18" s="10" t="n">
         <v>-6.2</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>17</v>
       </c>
-      <c r="J18" s="7" t="n">
+      <c r="K18" s="10" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="7" t="n">
+      <c r="M18" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="7" t="n">
+      <c r="O18" s="10" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="7" t="n">
+      <c r="Q18" s="10" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="7" t="n">
+      <c r="S18" s="10" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="7" t="n">
+      <c r="U18" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4961,58 +5068,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D19" s="9" t="inlineStr"/>
+      <c r="E19" s="10" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E19" s="7" t="n">
+      <c r="F19" s="10" t="n">
         <v>2.2</v>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="G19" s="10" t="n">
         <v>-15.2</v>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="H19" s="10" t="n">
         <v>-11.9</v>
       </c>
-      <c r="H19" s="7" t="n">
+      <c r="I19" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="7" t="n">
+      <c r="K19" s="10" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="7" t="n">
+      <c r="M19" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="7" t="n">
+      <c r="O19" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="7" t="n">
+      <c r="Q19" s="10" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="7" t="n">
+      <c r="S19" s="10" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="7" t="n">
+      <c r="U19" s="10" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5032,58 +5140,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="9" t="inlineStr"/>
+      <c r="E20" s="10" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E20" s="7" t="n">
+      <c r="F20" s="10" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="G20" s="10" t="n">
         <v>-1.3</v>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="H20" s="10" t="n">
         <v>-0.8</v>
       </c>
-      <c r="H20" s="7" t="n">
+      <c r="I20" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>6</v>
       </c>
-      <c r="J20" s="7" t="n">
+      <c r="K20" s="10" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="7" t="n">
+      <c r="M20" s="10" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="7" t="n">
+      <c r="O20" s="10" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="7" t="n">
+      <c r="Q20" s="10" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="7" t="n">
+      <c r="S20" s="10" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="7" t="n">
+      <c r="U20" s="10" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5103,58 +5212,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="9" t="inlineStr"/>
+      <c r="E21" s="10" t="n">
         <v>-2.4</v>
       </c>
-      <c r="E21" s="7" t="n">
+      <c r="F21" s="10" t="n">
         <v>-2.8</v>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="G21" s="10" t="n">
         <v>-8.5</v>
       </c>
-      <c r="G21" s="7" t="n">
+      <c r="H21" s="10" t="n">
         <v>11.9</v>
       </c>
-      <c r="H21" s="7" t="n">
+      <c r="I21" s="10" t="n">
         <v>29.3</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>4</v>
       </c>
-      <c r="J21" s="7" t="n">
+      <c r="K21" s="10" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="7" t="n">
+      <c r="M21" s="10" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="7" t="n">
+      <c r="O21" s="10" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="7" t="n">
+      <c r="Q21" s="10" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="7" t="n">
+      <c r="S21" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="7" t="n">
+      <c r="U21" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5174,58 +5284,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="9" t="inlineStr"/>
+      <c r="E22" s="10" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="F22" s="10" t="n">
         <v>-2</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="G22" s="10" t="n">
         <v>3.1</v>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="H22" s="10" t="n">
         <v>6.8</v>
       </c>
-      <c r="H22" s="7" t="n">
+      <c r="I22" s="10" t="n">
         <v>4.1</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>11</v>
       </c>
-      <c r="J22" s="7" t="n">
+      <c r="K22" s="10" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="7" t="n">
+      <c r="M22" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="7" t="n">
+      <c r="O22" s="10" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="7" t="n">
+      <c r="Q22" s="10" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="7" t="n">
+      <c r="S22" s="10" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="7" t="n">
+      <c r="U22" s="10" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5245,58 +5356,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="9" t="inlineStr"/>
+      <c r="E23" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="E23" s="7" t="n">
+      <c r="F23" s="10" t="n">
         <v>1.8</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="G23" s="10" t="n">
         <v>4.1</v>
       </c>
-      <c r="G23" s="7" t="n">
+      <c r="H23" s="10" t="n">
         <v>-2.7</v>
       </c>
-      <c r="H23" s="7" t="n">
+      <c r="I23" s="10" t="n">
         <v>3.3</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>14</v>
       </c>
-      <c r="J23" s="7" t="n">
+      <c r="K23" s="10" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="7" t="n">
+      <c r="M23" s="10" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="7" t="n">
+      <c r="O23" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="7" t="n">
+      <c r="Q23" s="10" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="7" t="n">
+      <c r="S23" s="10" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="7" t="n">
+      <c r="U23" s="10" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5316,58 +5428,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D24" s="9" t="inlineStr"/>
+      <c r="E24" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="E24" s="7" t="n">
+      <c r="F24" s="10" t="n">
         <v>1.6</v>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="G24" s="10" t="n">
         <v>8.5</v>
       </c>
-      <c r="G24" s="7" t="n">
+      <c r="H24" s="10" t="n">
         <v>1.7</v>
       </c>
-      <c r="H24" s="7" t="n">
+      <c r="I24" s="10" t="n">
         <v>3.7</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>13</v>
       </c>
-      <c r="J24" s="7" t="n">
+      <c r="K24" s="10" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="7" t="n">
+      <c r="M24" s="10" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="7" t="n">
+      <c r="O24" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="7" t="n">
+      <c r="Q24" s="10" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="7" t="n">
+      <c r="S24" s="10" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="7" t="n">
+      <c r="U24" s="10" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5387,58 +5500,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="7" t="n">
+      <c r="D25" s="9" t="inlineStr"/>
+      <c r="E25" s="10" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="F25" s="10" t="n">
         <v>4.2</v>
       </c>
-      <c r="F25" s="7" t="n">
+      <c r="G25" s="10" t="n">
         <v>7.4</v>
       </c>
-      <c r="G25" s="7" t="n">
+      <c r="H25" s="10" t="n">
         <v>-2.4</v>
       </c>
-      <c r="H25" s="7" t="n">
+      <c r="I25" s="10" t="n">
         <v>16.1</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>9</v>
       </c>
-      <c r="J25" s="7" t="n">
+      <c r="K25" s="10" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="7" t="n">
+      <c r="M25" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="7" t="n">
+      <c r="O25" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="7" t="n">
+      <c r="Q25" s="10" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="7" t="n">
+      <c r="S25" s="10" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="7" t="n">
+      <c r="U25" s="10" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5458,58 +5572,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D26" s="9" t="inlineStr"/>
+      <c r="E26" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="F26" s="10" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="G26" s="10" t="n">
         <v>2.9</v>
       </c>
-      <c r="G26" s="7" t="n">
+      <c r="H26" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="H26" s="7" t="n">
+      <c r="I26" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>15</v>
       </c>
-      <c r="J26" s="7" t="n">
+      <c r="K26" s="10" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="7" t="n">
+      <c r="M26" s="10" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="7" t="n">
+      <c r="O26" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="7" t="n">
+      <c r="Q26" s="10" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="7" t="n">
+      <c r="S26" s="10" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="7" t="n">
+      <c r="U26" s="10" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5529,58 +5644,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="7" t="n">
+      <c r="D27" s="9" t="inlineStr"/>
+      <c r="E27" s="10" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E27" s="7" t="n">
+      <c r="F27" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="F27" s="7" t="n">
+      <c r="G27" s="10" t="n">
         <v>13.6</v>
       </c>
-      <c r="G27" s="7" t="n">
+      <c r="H27" s="10" t="n">
         <v>29.1</v>
       </c>
-      <c r="H27" s="7" t="n">
+      <c r="I27" s="10" t="n">
         <v>50.7</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="7" t="n">
+      <c r="K27" s="10" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="7" t="n">
+      <c r="M27" s="10" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="7" t="n">
+      <c r="O27" s="10" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="7" t="n">
+      <c r="Q27" s="10" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="7" t="n">
+      <c r="S27" s="10" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="7" t="n">
+      <c r="U27" s="10" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5600,58 +5716,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="D28" s="9" t="inlineStr"/>
+      <c r="E28" s="10" t="n">
         <v>1.4</v>
       </c>
-      <c r="E28" s="7" t="n">
+      <c r="F28" s="10" t="n">
         <v>3.8</v>
       </c>
-      <c r="F28" s="7" t="n">
+      <c r="G28" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="H28" s="10" t="n">
         <v>18.1</v>
       </c>
-      <c r="H28" s="7" t="n">
+      <c r="I28" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>3</v>
       </c>
-      <c r="J28" s="7" t="n">
+      <c r="K28" s="10" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="7" t="n">
+      <c r="M28" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="7" t="n">
+      <c r="O28" s="10" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="7" t="n">
+      <c r="Q28" s="10" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="7" t="n">
+      <c r="S28" s="10" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="7" t="n">
+      <c r="U28" s="10" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5671,58 +5788,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="7" t="n">
+      <c r="D29" s="9" t="inlineStr"/>
+      <c r="E29" s="10" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E29" s="7" t="n">
+      <c r="F29" s="10" t="n">
         <v>-1.9</v>
       </c>
-      <c r="F29" s="7" t="n">
+      <c r="G29" s="10" t="n">
         <v>5.4</v>
       </c>
-      <c r="G29" s="7" t="n">
+      <c r="H29" s="10" t="n">
         <v>-10.8</v>
       </c>
-      <c r="H29" s="7" t="n">
+      <c r="I29" s="10" t="n">
         <v>-2.2</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>16</v>
       </c>
-      <c r="J29" s="7" t="n">
+      <c r="K29" s="10" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="7" t="n">
+      <c r="M29" s="10" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="7" t="n">
+      <c r="O29" s="10" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="7" t="n">
+      <c r="Q29" s="10" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="7" t="n">
+      <c r="S29" s="10" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="7" t="n">
+      <c r="U29" s="10" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -5742,24 +5860,25 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr"/>
-      <c r="E30" s="7" t="inlineStr"/>
-      <c r="F30" s="7" t="inlineStr"/>
-      <c r="G30" s="7" t="inlineStr"/>
-      <c r="H30" s="7" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" s="7" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" s="7" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" s="7" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" s="7" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" s="7" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" s="7" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+      <c r="D30" s="9" t="inlineStr"/>
+      <c r="E30" s="10" t="inlineStr"/>
+      <c r="F30" s="10" t="inlineStr"/>
+      <c r="G30" s="10" t="inlineStr"/>
+      <c r="H30" s="10" t="inlineStr"/>
+      <c r="I30" s="10" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" s="10" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="10" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" s="10" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" s="10" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" s="10" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" s="10" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5777,24 +5896,25 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr"/>
-      <c r="E31" s="7" t="inlineStr"/>
-      <c r="F31" s="7" t="inlineStr"/>
-      <c r="G31" s="7" t="inlineStr"/>
-      <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" s="7" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" s="7" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" s="7" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" s="7" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" s="7" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" s="7" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
+      <c r="D31" s="9" t="inlineStr"/>
+      <c r="E31" s="10" t="inlineStr"/>
+      <c r="F31" s="10" t="inlineStr"/>
+      <c r="G31" s="10" t="inlineStr"/>
+      <c r="H31" s="10" t="inlineStr"/>
+      <c r="I31" s="10" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" s="10" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="10" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" s="10" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" s="10" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" s="10" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" s="10" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5812,24 +5932,25 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr"/>
-      <c r="E32" s="7" t="inlineStr"/>
-      <c r="F32" s="7" t="inlineStr"/>
-      <c r="G32" s="7" t="inlineStr"/>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" s="7" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" s="7" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" s="7" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" s="7" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" s="7" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="D32" s="9" t="inlineStr"/>
+      <c r="E32" s="10" t="inlineStr"/>
+      <c r="F32" s="10" t="inlineStr"/>
+      <c r="G32" s="10" t="inlineStr"/>
+      <c r="H32" s="10" t="inlineStr"/>
+      <c r="I32" s="10" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" s="10" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="10" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" s="10" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" s="10" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" s="10" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" s="10" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5847,24 +5968,29 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr"/>
-      <c r="E33" s="7" t="inlineStr"/>
-      <c r="F33" s="7" t="inlineStr"/>
-      <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" s="7" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" s="7" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" s="7" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" s="7" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" s="7" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" s="7" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>반도체: 당일 ETF 시세 수집 실패(공란). 섹터 순강도 약세(-1), AI·반도체 차익실현 추정</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr"/>
+      <c r="G33" s="10" t="inlineStr"/>
+      <c r="H33" s="10" t="inlineStr"/>
+      <c r="I33" s="10" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" s="10" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="10" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" s="10" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" s="10" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" s="10" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" s="10" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5882,24 +6008,29 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr"/>
-      <c r="E34" s="7" t="inlineStr"/>
-      <c r="F34" s="7" t="inlineStr"/>
-      <c r="G34" s="7" t="inlineStr"/>
-      <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" s="7" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" s="7" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" s="7" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" s="7" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" s="7" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>테크: 당일 ETF 시세 수집 실패(공란). 테크서비스 순강도 -1 약세 추정</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr"/>
+      <c r="F34" s="10" t="inlineStr"/>
+      <c r="G34" s="10" t="inlineStr"/>
+      <c r="H34" s="10" t="inlineStr"/>
+      <c r="I34" s="10" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" s="10" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="10" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" s="10" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" s="10" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" s="10" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" s="10" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5917,24 +6048,29 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr"/>
-      <c r="E35" s="7" t="inlineStr"/>
-      <c r="F35" s="7" t="inlineStr"/>
-      <c r="G35" s="7" t="inlineStr"/>
-      <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" s="7" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" s="7" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" s="7" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" s="7" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" s="7" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>5G통신: 당일 ETF 시세 수집 실패(공란). 통신 순강도 중립 추정</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr"/>
+      <c r="F35" s="10" t="inlineStr"/>
+      <c r="G35" s="10" t="inlineStr"/>
+      <c r="H35" s="10" t="inlineStr"/>
+      <c r="I35" s="10" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" s="10" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="10" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" s="10" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" s="10" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" s="10" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" s="10" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5952,24 +6088,29 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr"/>
-      <c r="E36" s="7" t="inlineStr"/>
-      <c r="F36" s="7" t="inlineStr"/>
-      <c r="G36" s="7" t="inlineStr"/>
-      <c r="H36" s="7" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" s="7" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" s="7" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" s="7" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" s="7" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" s="7" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" s="7" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>신에너지차: 당일 ETF 시세 수집 실패(공란). 순강도 중립 추정</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr"/>
+      <c r="F36" s="10" t="inlineStr"/>
+      <c r="G36" s="10" t="inlineStr"/>
+      <c r="H36" s="10" t="inlineStr"/>
+      <c r="I36" s="10" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" s="10" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="10" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" s="10" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" s="10" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" s="10" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" s="10" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5987,24 +6128,29 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr"/>
-      <c r="E37" s="7" t="inlineStr"/>
-      <c r="F37" s="7" t="inlineStr"/>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" s="7" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" s="7" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" s="7" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" s="7" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" s="7" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" s="7" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>방산: 당일 ETF 시세 수집 실패(공란). 순강도 중립 추정</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr"/>
+      <c r="F37" s="10" t="inlineStr"/>
+      <c r="G37" s="10" t="inlineStr"/>
+      <c r="H37" s="10" t="inlineStr"/>
+      <c r="I37" s="10" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" s="10" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="10" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" s="10" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" s="10" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" s="10" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" s="10" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6022,24 +6168,29 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr"/>
-      <c r="E38" s="7" t="inlineStr"/>
-      <c r="F38" s="7" t="inlineStr"/>
-      <c r="G38" s="7" t="inlineStr"/>
-      <c r="H38" s="7" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" s="7" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" s="7" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" s="7" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" s="7" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" s="7" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" s="7" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>태양광: 당일 ETF 시세 수집 실패(공란). 순강도 중립 추정</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr"/>
+      <c r="F38" s="10" t="inlineStr"/>
+      <c r="G38" s="10" t="inlineStr"/>
+      <c r="H38" s="10" t="inlineStr"/>
+      <c r="I38" s="10" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" s="10" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="10" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" s="10" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" s="10" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" s="10" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" s="10" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6057,24 +6208,29 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr"/>
-      <c r="E39" s="7" t="inlineStr"/>
-      <c r="F39" s="7" t="inlineStr"/>
-      <c r="G39" s="7" t="inlineStr"/>
-      <c r="H39" s="7" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" s="7" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" s="7" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" s="7" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" s="7" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" s="7" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" s="7" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>백주(주류): 당일 ETF 시세 수집 실패(공란). 순강도 중립 추정</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr"/>
+      <c r="F39" s="10" t="inlineStr"/>
+      <c r="G39" s="10" t="inlineStr"/>
+      <c r="H39" s="10" t="inlineStr"/>
+      <c r="I39" s="10" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" s="10" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="10" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" s="10" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" s="10" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" s="10" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" s="10" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6092,24 +6248,29 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr"/>
-      <c r="E40" s="7" t="inlineStr"/>
-      <c r="F40" s="7" t="inlineStr"/>
-      <c r="G40" s="7" t="inlineStr"/>
-      <c r="H40" s="7" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" s="7" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" s="7" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" s="7" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" s="7" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" s="7" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" s="7" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>은행: 당일 ETF 시세 수집 실패(공란). 금융 순강도 중립 추정</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr"/>
+      <c r="F40" s="10" t="inlineStr"/>
+      <c r="G40" s="10" t="inlineStr"/>
+      <c r="H40" s="10" t="inlineStr"/>
+      <c r="I40" s="10" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" s="10" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="10" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" s="10" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" s="10" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" s="10" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" s="10" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6127,24 +6288,29 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr"/>
-      <c r="E41" s="7" t="inlineStr"/>
-      <c r="F41" s="7" t="inlineStr"/>
-      <c r="G41" s="7" t="inlineStr"/>
-      <c r="H41" s="7" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" s="7" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" s="7" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" s="7" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" s="7" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" s="7" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" s="7" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>유색금속: 당일 ETF 시세 수집 실패(공란). 비철금속 순강도 중립 추정</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr"/>
+      <c r="F41" s="10" t="inlineStr"/>
+      <c r="G41" s="10" t="inlineStr"/>
+      <c r="H41" s="10" t="inlineStr"/>
+      <c r="I41" s="10" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" s="10" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="10" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" s="10" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" s="10" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" s="10" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" s="10" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6162,24 +6328,29 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr"/>
-      <c r="E42" s="7" t="inlineStr"/>
-      <c r="F42" s="7" t="inlineStr"/>
-      <c r="G42" s="7" t="inlineStr"/>
-      <c r="H42" s="7" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" s="7" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" s="7" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" s="7" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" s="7" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" s="7" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" s="7" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>부동산: 당일 ETF 시세 수집 실패(공란). 순강도 중립 추정</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr"/>
+      <c r="F42" s="10" t="inlineStr"/>
+      <c r="G42" s="10" t="inlineStr"/>
+      <c r="H42" s="10" t="inlineStr"/>
+      <c r="I42" s="10" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" s="10" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="10" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" s="10" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" s="10" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" s="10" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" s="10" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6197,24 +6368,29 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr"/>
-      <c r="E43" s="7" t="inlineStr"/>
-      <c r="F43" s="7" t="inlineStr"/>
-      <c r="G43" s="7" t="inlineStr"/>
-      <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" s="7" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" s="7" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" s="7" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" s="7" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" s="7" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" s="7" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>증권: 당일 ETF 시세 수집 실패(공란). 지수 -1.6% 조정 속 약세 추정</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr"/>
+      <c r="F43" s="10" t="inlineStr"/>
+      <c r="G43" s="10" t="inlineStr"/>
+      <c r="H43" s="10" t="inlineStr"/>
+      <c r="I43" s="10" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" s="10" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="10" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" s="10" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" s="10" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" s="10" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" s="10" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6232,24 +6408,29 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr"/>
-      <c r="E44" s="7" t="inlineStr"/>
-      <c r="F44" s="7" t="inlineStr"/>
-      <c r="G44" s="7" t="inlineStr"/>
-      <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" s="7" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" s="7" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" s="7" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" s="7" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" s="7" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" s="7" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>의약: 당일 ETF 시세 수집 실패(공란). 헬스 순강도 중립 추정</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr"/>
+      <c r="F44" s="10" t="inlineStr"/>
+      <c r="G44" s="10" t="inlineStr"/>
+      <c r="H44" s="10" t="inlineStr"/>
+      <c r="I44" s="10" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" s="10" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="10" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" s="10" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" s="10" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" s="10" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" s="10" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6267,24 +6448,29 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr"/>
-      <c r="E45" s="7" t="inlineStr"/>
-      <c r="F45" s="7" t="inlineStr"/>
-      <c r="G45" s="7" t="inlineStr"/>
-      <c r="H45" s="7" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" s="7" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" s="7" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" s="7" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" s="7" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" s="7" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" s="7" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>소비: 당일 ETF 시세 수집 실패(공란). 순강도 중립 추정</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr"/>
+      <c r="F45" s="10" t="inlineStr"/>
+      <c r="G45" s="10" t="inlineStr"/>
+      <c r="H45" s="10" t="inlineStr"/>
+      <c r="I45" s="10" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" s="10" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="10" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" s="10" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" s="10" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" s="10" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" s="10" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6294,7 +6480,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-2.4"/>
@@ -6306,7 +6492,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-5.2"/>
@@ -6318,7 +6504,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-15.2"/>
@@ -6330,7 +6516,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-11.9"/>
@@ -6342,7 +6528,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-9.199999999999999"/>
@@ -6354,7 +6540,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -6364,7 +6550,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -6374,7 +6560,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-7.2"/>
@@ -6386,7 +6572,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.6"/>
@@ -6398,7 +6584,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-8.4"/>
@@ -6410,7 +6596,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -6518,12 +6704,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6562,15 +6748,19 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="9" t="inlineStr"/>
+      <c r="M2" s="11" t="inlineStr">
+        <is>
+          <t>(연료전지): AI데이터센터 납품 지연 경고·오라클 뉴멕시코 허가 불허로 AI전력주 급락</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6609,15 +6799,19 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="9" t="inlineStr"/>
+      <c r="M3" s="11" t="inlineStr">
+        <is>
+          <t>(소형 로켓발사): 이리듐 인수 딜 밸류 부담·스페이스X 경쟁 부각에 우주주 매도</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6658,15 +6852,19 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="9" t="inlineStr"/>
+      <c r="M4" s="11" t="inlineStr">
+        <is>
+          <t>(광섬유·특수유리): 7/28 실적 앞두고 통신 설비투자 둔화·보수적 가이던스 경계</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6707,15 +6905,19 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="9" t="inlineStr"/>
+      <c r="M5" s="11" t="inlineStr">
+        <is>
+          <t>(반도체 파운드리): 내부자 주식매도 공시·고평가 논란 속 반도체 조정 연장</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6760,15 +6962,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr"/>
+      <c r="M6" s="11" t="inlineStr">
+        <is>
+          <t>(모빌리티 플랫폼): 웨이모 협력 종료 검토 보도(FT)에 로보택시 경쟁 우려·신저가</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6809,15 +7015,15 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="9" t="inlineStr"/>
+      <c r="M7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6858,15 +7064,15 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="9" t="inlineStr"/>
+      <c r="M8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6905,15 +7111,15 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="9" t="inlineStr"/>
+      <c r="M9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6952,15 +7158,15 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="9" t="inlineStr"/>
+      <c r="M10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6999,15 +7205,15 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="9" t="inlineStr"/>
+      <c r="M11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7050,15 +7256,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M12" s="9" t="inlineStr"/>
+      <c r="M12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7097,15 +7303,15 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="9" t="inlineStr"/>
+      <c r="M13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7144,10 +7350,10 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="9" t="inlineStr"/>
+      <c r="M14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7197,10 +7403,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M15" s="9" t="inlineStr"/>
+      <c r="M15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7250,10 +7456,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M16" s="9" t="inlineStr"/>
+      <c r="M16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7299,10 +7505,10 @@
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" s="9" t="inlineStr"/>
+      <c r="M17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7348,14 +7554,14 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="9" t="inlineStr">
+      <c r="M18" s="11" t="inlineStr">
         <is>
           <t>(전일) (모바일 광고 플랫폼·AXON AI): AXON 셀프서브 전환 마진 희석 우려·CEO 지분매각, 광고 경쟁 심화</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7399,10 +7605,10 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="9" t="inlineStr"/>
+      <c r="M19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7448,10 +7654,10 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="9" t="inlineStr"/>
+      <c r="M20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7497,10 +7703,10 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="9" t="inlineStr"/>
+      <c r="M21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7550,10 +7756,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M22" s="9" t="inlineStr"/>
+      <c r="M22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7599,15 +7805,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M23" s="9" t="inlineStr"/>
+      <c r="M23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7646,15 +7852,19 @@
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" s="9" t="inlineStr"/>
+      <c r="M24" s="11" t="inlineStr">
+        <is>
+          <t>(병원운영): 2Q EPS $6.12로 예상 43% 상회, 연간가이던스 상향·자사주매입 $20억 확대</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7693,15 +7903,19 @@
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" s="9" t="inlineStr"/>
+      <c r="M25" s="11" t="inlineStr">
+        <is>
+          <t>(포장지·컨테이너보드): RBC·Truist 목표가 상향, 북미 공급 타이트·가격 반등 기대</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7742,15 +7956,19 @@
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" s="9" t="inlineStr"/>
+      <c r="M26" s="11" t="inlineStr">
+        <is>
+          <t>(골판지 포장재): 대형 패키징 계약·섹터 전반 포장지 가격 상승 모멘텀</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7791,15 +8009,19 @@
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="9" t="inlineStr"/>
+      <c r="M27" s="11" t="inlineStr">
+        <is>
+          <t>(데이터센터 REIT): 2Q FFO $2.13 대폭 상회, 가이던스 상향·AI 임대수요 사상최대</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7838,15 +8060,19 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="9" t="inlineStr"/>
+      <c r="M28" s="11" t="inlineStr">
+        <is>
+          <t>(금융소프트웨어): 2Q 조정EPS $1.76 사상최대, 유기성장 7.6%·가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7889,15 +8115,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M29" s="9" t="inlineStr"/>
+      <c r="M29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7938,15 +8164,15 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="9" t="inlineStr"/>
+      <c r="M30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7991,15 +8217,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M31" s="9" t="inlineStr"/>
+      <c r="M31" s="11" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8044,15 +8270,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M32" s="9" t="inlineStr"/>
+      <c r="M32" s="11" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8097,15 +8323,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M33" s="9" t="inlineStr"/>
+      <c r="M33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8150,15 +8376,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M34" s="9" t="inlineStr"/>
+      <c r="M34" s="11" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8199,15 +8425,15 @@
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" s="9" t="inlineStr"/>
+      <c r="M35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8252,15 +8478,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M36" s="9" t="inlineStr"/>
+      <c r="M36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8305,15 +8531,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M37" s="9" t="inlineStr"/>
+      <c r="M37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8352,15 +8578,15 @@
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" s="9" t="inlineStr"/>
+      <c r="M38" s="11" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8399,15 +8625,15 @@
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" s="9" t="inlineStr"/>
+      <c r="M39" s="11" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8452,15 +8678,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M40" s="9" t="inlineStr"/>
+      <c r="M40" s="11" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8501,15 +8727,15 @@
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" s="9" t="inlineStr"/>
+      <c r="M41" s="11" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8550,15 +8776,15 @@
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" s="9" t="inlineStr"/>
+      <c r="M42" s="11" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8603,15 +8829,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M43" s="9" t="inlineStr"/>
+      <c r="M43" s="11" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8652,15 +8878,15 @@
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr"/>
+      <c r="M44" s="11" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8705,15 +8931,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M45" s="9" t="inlineStr"/>
+      <c r="M45" s="11" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8758,15 +8984,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M46" s="9" t="inlineStr"/>
+      <c r="M46" s="11" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8807,15 +9033,15 @@
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" s="9" t="inlineStr"/>
+      <c r="M47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8860,15 +9086,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M48" s="9" t="inlineStr"/>
+      <c r="M48" s="11" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8909,15 +9135,15 @@
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" s="9" t="inlineStr"/>
+      <c r="M49" s="11" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8962,15 +9188,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M50" s="9" t="inlineStr"/>
+      <c r="M50" s="11" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9015,15 +9241,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M51" s="9" t="inlineStr"/>
+      <c r="M51" s="11" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9064,15 +9290,15 @@
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" s="9" t="inlineStr"/>
+      <c r="M52" s="11" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9113,15 +9339,15 @@
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" s="9" t="inlineStr"/>
+      <c r="M53" s="11" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9166,15 +9392,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M54" s="9" t="inlineStr"/>
+      <c r="M54" s="11" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9219,15 +9445,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M55" s="9" t="inlineStr"/>
+      <c r="M55" s="11" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9272,15 +9498,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M56" s="9" t="inlineStr"/>
+      <c r="M56" s="11" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9325,15 +9551,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M57" s="9" t="inlineStr"/>
+      <c r="M57" s="11" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9378,15 +9604,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M58" s="9" t="inlineStr"/>
+      <c r="M58" s="11" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9431,15 +9657,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M59" s="9" t="inlineStr"/>
+      <c r="M59" s="11" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9480,15 +9706,15 @@
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" s="9" t="inlineStr"/>
+      <c r="M60" s="11" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9529,15 +9755,15 @@
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" s="9" t="inlineStr"/>
+      <c r="M61" s="11" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9580,15 +9806,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M62" s="9" t="inlineStr"/>
+      <c r="M62" s="11" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9629,15 +9855,15 @@
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" s="9" t="inlineStr"/>
+      <c r="M63" s="11" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9682,15 +9908,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M64" s="9" t="inlineStr"/>
+      <c r="M64" s="11" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9731,10 +9957,10 @@
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" s="9" t="inlineStr"/>
+      <c r="M65" s="11" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9784,10 +10010,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M66" s="9" t="inlineStr"/>
+      <c r="M66" s="11" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9837,10 +10063,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M67" s="9" t="inlineStr"/>
+      <c r="M67" s="11" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9886,10 +10112,10 @@
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" s="9" t="inlineStr"/>
+      <c r="M68" s="11" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9937,10 +10163,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M69" s="9" t="inlineStr"/>
+      <c r="M69" s="11" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+      <c r="A70" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9990,10 +10216,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M70" s="9" t="inlineStr"/>
+      <c r="M70" s="11" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10043,10 +10269,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M71" s="9" t="inlineStr"/>
+      <c r="M71" s="11" t="inlineStr">
+        <is>
+          <t>(방산·항공엔진): 2Q 매출 $247억(+14%)·수주잔고 $2890억 사상최대, 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10092,10 +10322,10 @@
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" s="9" t="inlineStr"/>
+      <c r="M72" s="11" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10145,14 +10375,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M73" s="9" t="inlineStr">
+      <c r="M73" s="11" t="inlineStr">
         <is>
           <t>(전일) (철도·화물 운송장비): Q2 매출 $31.8억(+17.5%)·EPS $2.76 상회, 수주잔고 $309억(+41.7%)에 가이던스 상향</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="A74" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10202,10 +10432,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M74" s="9" t="inlineStr"/>
+      <c r="M74" s="11" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="A75" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10255,10 +10485,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M75" s="9" t="inlineStr"/>
+      <c r="M75" s="11" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10308,14 +10538,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M76" s="9" t="inlineStr">
+      <c r="M76" s="11" t="inlineStr">
         <is>
           <t>(전일) (대형트럭 제조·켄워스·피터빌트): 6월 Class8 트럭 수주 전년비 +230% 급증, 수요 회복 기대</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10365,10 +10595,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M77" s="9" t="inlineStr"/>
+      <c r="M77" s="11" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+      <c r="A78" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10418,10 +10648,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M78" s="9" t="inlineStr"/>
+      <c r="M78" s="11" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
+      <c r="A79" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10467,10 +10697,10 @@
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
-      <c r="M79" s="9" t="inlineStr"/>
+      <c r="M79" s="11" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10520,10 +10750,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M80" s="9" t="inlineStr"/>
+      <c r="M80" s="11" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10573,10 +10803,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M81" s="9" t="inlineStr"/>
+      <c r="M81" s="11" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10626,10 +10856,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M82" s="9" t="inlineStr"/>
+      <c r="M82" s="11" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="A83" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10679,10 +10909,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M83" s="9" t="inlineStr"/>
+      <c r="M83" s="11" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="A84" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10732,10 +10962,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M84" s="9" t="inlineStr"/>
+      <c r="M84" s="11" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+      <c r="A85" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10785,10 +11015,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M85" s="9" t="inlineStr"/>
+      <c r="M85" s="11" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10838,7 +11068,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M86" s="9" t="inlineStr"/>
+      <c r="M86" s="11" t="inlineStr">
+        <is>
+          <t>(지역은행): 2Q EPS 42% 상회에도 3Q 순이자마진 바닥 전망에 차익실현 매도</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M86"/>
@@ -10938,7 +11172,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10984,10 +11218,14 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="9" t="inlineStr"/>
+      <c r="M2" s="11" t="inlineStr">
+        <is>
+          <t>(반도체 절단·연마장비): 2Q 순이익 가이던스 395억엔이 시장 예상 하회, 실망 매물로 급락</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11033,10 +11271,10 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="9" t="inlineStr"/>
+      <c r="M3" s="11" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11080,10 +11318,10 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="9" t="inlineStr"/>
+      <c r="M4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11129,10 +11367,10 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="9" t="inlineStr"/>
+      <c r="M5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11182,10 +11420,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr"/>
+      <c r="M6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11235,10 +11473,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr"/>
+      <c r="M7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11288,10 +11526,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M8" s="9" t="inlineStr"/>
+      <c r="M8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11337,14 +11575,14 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="M9" s="11" t="inlineStr">
         <is>
           <t>(전일) 닛폰스틸(일본 최대 철강): US스틸 철강가 호조·FY27 이익 1000억엔 기여 기대로 자율반등</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11394,10 +11632,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M10" s="9" t="inlineStr"/>
+      <c r="M10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11447,10 +11685,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M11" s="9" t="inlineStr"/>
+      <c r="M11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11500,10 +11738,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M12" s="9" t="inlineStr"/>
+      <c r="M12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11553,10 +11791,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M13" s="9" t="inlineStr"/>
+      <c r="M13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11606,10 +11844,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M14" s="9" t="inlineStr"/>
+      <c r="M14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11659,14 +11897,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M15" s="9" t="inlineStr">
+      <c r="M15" s="11" t="inlineStr">
         <is>
           <t>(전일) (손해보험 지주): 장기금리 상승에 보험자산 운용이익 개선 기대, 금융섹터 강세에 동반 신고가</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11712,14 +11950,14 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="9" t="inlineStr">
+      <c r="M16" s="11" t="inlineStr">
         <is>
           <t>(전일) 캐논(카메라·사무기기·반도체 노광): 광범위 자율반등+7/27 결산 앞둔 매수</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11769,7 +12007,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M17" s="9" t="inlineStr">
+      <c r="M17" s="11" t="inlineStr">
         <is>
           <t>(전일) (우편계열 은행): 일본 장기금리 약 29년래 고수준(~2.8%) 이자마진 확대 기대로 금융섹터 매수 유입</t>
         </is>
@@ -11873,7 +12111,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11919,10 +12157,10 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="9" t="inlineStr"/>
+      <c r="M2" s="11" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11966,10 +12204,10 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="9" t="inlineStr"/>
+      <c r="M3" s="11" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12019,10 +12257,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr"/>
+      <c r="M4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12068,14 +12306,14 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="M5" s="11" t="inlineStr">
         <is>
           <t>(전일) (글로벌 항암제 개발): 비원메디슨, 특별한 뉴스 없음(브루킨사·소노로토클락스 파이프라인 모멘텀 지속 추정)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12125,10 +12363,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr"/>
+      <c r="M6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12174,14 +12412,14 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="11" t="inlineStr">
         <is>
           <t>(전일) (홍콩 통신사): HKT, 특별한 뉴스 없음(방어주 성격·AI 데이터센터 인프라 테마 수급 추정)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12231,14 +12469,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M8" s="9" t="inlineStr">
+      <c r="M8" s="11" t="inlineStr">
         <is>
           <t>(전일) (홍콩 국적 항공사): 캐세이퍼시픽, 상반기 순이익 60~65억 홍콩달러(전년비 최대 +76%) 예고, 여객·화물 호조</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12284,10 +12522,10 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="9" t="inlineStr"/>
+      <c r="M9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12337,7 +12575,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M10" s="9" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>(전일) SITC(아시아 역내 컨테이너 해운): 컨테이너 운임 4년래 고점·중동 리스크로 역내 운임 반등 수혜</t>
         </is>
@@ -12441,7 +12679,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12485,10 +12723,14 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="9" t="inlineStr"/>
+      <c r="M2" s="11" t="inlineStr">
+        <is>
+          <t>(낸드·디램 스토리지모듈): 8거래일 6하한가 연속 급락, 2분기 순이익 최대 -30% 우려에 고점 대비 -58%서 추가 하락</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12534,10 +12776,10 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="9" t="inlineStr"/>
+      <c r="M3" s="11" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12583,10 +12825,10 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="9" t="inlineStr"/>
+      <c r="M4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12632,10 +12874,10 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="9" t="inlineStr"/>
+      <c r="M5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12683,10 +12925,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr"/>
+      <c r="M6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12736,10 +12978,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr"/>
+      <c r="M7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12785,10 +13027,10 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="9" t="inlineStr"/>
+      <c r="M8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12838,10 +13080,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M9" s="9" t="inlineStr"/>
+      <c r="M9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12887,7 +13129,7 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="9" t="inlineStr"/>
+      <c r="M10" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M10"/>
